--- a/extenbooks/ES1103.xlsx
+++ b/extenbooks/ES1103.xlsx
@@ -793,11 +793,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -957,7 +957,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1103 — Social Tax Rate (ST 1987) — PENDING</t>
+          <t># ES1103 — Social Tax Rate (S&amp;T 1987)</t>
         </is>
       </c>
     </row>
@@ -969,87 +969,31 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: book_period_validated. Derived: `S604 / S617`. Range 1952-1989: [0.2616, 0.3627]. Workers pay 26-36% of total compensation back to state via taxes. The MAGNITUDE of this rate vs ES1102 tells you whether NSW is net positive or negative.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>derived from Ch6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Compute T_w / EC using S604 + employee compensation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1103.xlsx
+++ b/extenbooks/ES1103.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1985</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -946,54 +946,459 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1103-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh &amp; Tonak 1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1103 — Social Tax Rate (S&amp;T 1987)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated. Derived: `S604 / S617`. Range 1952-1989: [0.2616, 0.3627]. Workers pay 26-36% of total compensation back to state via taxes. The MAGNITUDE of this rate vs ES1102 tells you whether NSW is net positive or negative.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1103 — Social Tax Rate (Shaikh &amp; Tonak 1987)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion.*</t>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>- **SID**: ES1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>- **Name**: Social Tax Rate (ST 1987)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- **Study**: `study_02_st_1987` — Shaikh &amp; Tonak (1987) "The Welfare State and the Myth of the Social Wage" in Cherry et al. eds., *The Imperiled Economy*, Book I, pp.184-194</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>- **Chapter**: ES-prefix follow-up study (registry chapter index 11; book equivalent is the 1987 ST paper, not the 1994 book)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **Status**: `book_period_validated` (1952-1985 annual; Wave-2 / Stage-4 extension to 1986-2024 pending NIPA Group I/II reconstruction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- **Units**: ratio (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES1103 implements the comprehensive social tax rate defined in Shaikh &amp; Tonak (1987). The construction divides total taxes paid by workers (`S604 = T_w`) by total employee compensation (`S617 = EC`), yielding a dimensionless rate. The verbatim primary anchor for the numerator is **"Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)"** (Shaikh &amp; Tonak 1987, Empirical Methodology, p.187). The data source is the book's Appendix Table 1 (p.191, the 1964 illustration) and Table 2 (p.192, the full 1952-1985 annual taxes-paid-by-labor column), cross-checked against BEA *Survey of Current Business* 1981 tables at pp.121, 123, 129, 134, and 170.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The numerator `T_w` aggregates two groups. Group I (100% from workers — flows directly from employee compensation) comprises: Employer + Employee Contributions for Social Insurance, Other Labor Income (pension contributions), and the small net receipts from government-administered lotteries and parimutuels (treated as a positive net tax, sign-inverted from BEA's listing because the net receipts are consistently positive to the state). Group II (allocated by labor share = total labor income ÷ personal income) comprises: federal and state personal income taxes, motor vehicle licenses, the home-owner portion of property taxes, and miscellaneous other taxes and non-taxes. The 1964 illustration in Appendix Table 1 yields: Group I (28.66 + 0.002 = 28.662) plus Group II (36.51 + 2.60 + 0.78 + 5.99 = 45.88) = total `T_w = 74.52B` in 1964. Corporate profit taxes, indirect business taxes, and estate and gift taxes are excluded as not levied on workers. The denominator (`EC`) is computed at the cost-to-capitalists level — wages and benefits plus employer Social Security contributions plus Other Labor Income — so that the employer SS contribution appears in both numerator and denominator, correctly reflecting that it is a labor cost workers bear via reduced take-home pay. The verbatim trajectory anchor is **"Tax Rate: 1952: ~0.17 (17%) … Rises slowly and steadily throughout period … 1968: ~0.22 (22%) … 1975: ~0.24 (24%) … 1984: ~0.31 (31%) … By 1984: Reaches all-time high (41% higher than 1966)"** (Shaikh &amp; Tonak 1987, Figure 2 description, p.188).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>The transformation produces a monotonically rising rate over 1952-1985 (~17% → ~31%), driven primarily by Social Security expansion rather than income-tax policy. The Reagan-era income tax cuts were offset by continuing growth in social security contributions, so by 1985 the rate reached 41% above its 1966 level despite income-tax rate reductions — illustrating that the social-security component dominates the long-run trend. The substantive interpretive thrust the rising tax rate supports is the rebuttal of the Bowles &amp; Gintis "rising social wage" thesis: **"Arguments such as those of Bowles and Gintis, which claim that 'there has been a substantial redistribution from capital to labor' over the postwar period, and which trace the current economic crisis back to a supposed increased social wage, appear to be quite ill-founded."** (Shaikh &amp; Tonak 1987, p.187). Validation runs against book benchmarks in Figure 2 and Table 2 (1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31) within the rate-series tolerance class; the V03 validator additionally enforces the expected range `[0.0, 0.3]`. Comparison with BLS spendable-earnings-derived series (Bowles &amp; Gintis) is intentionally not used as validation because BLS omits state and local taxes — Bowles &amp; Gintis's 1977 tax estimate was $10/week vs Tonak's $30.42/week, a two-thirds underestimate documented in note 5 (p.193).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Technical/Knowledge_Base/external_papers/productive_labor/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md` (full ST 1987 paper extraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>- Book tables: ST 1987 Appendix Table 1 (1964 illustration, p.191); ST 1987 Table 2 (taxes column, 1952-1985 annual, p.192); ST 1987 Figure 2 (tax rate trajectory, p.188); ST 1987 Figure 1 (broader social-wage decomposition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>- External sources: BEA Survey of Current Business 1981, tables at pp.121, 123, 129, 134 (tax data); BEA SCB 1981 p.170 (lotteries/parimutuels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>- Upstream series: S604 (taxes paid by workers T_w), S617 (employee compensation EC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>- Companion ES series in the same study: ES1101 (benefits to workers B_w), ES1102 (government transfers G_w), and ES1001/ES1002 (related)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>- Related: Tonak (1984) PhD dissertation "A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980", UMI Order #9414212 — the underlying comprehensive tax accounting framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- 34 annual observations 1952-1985</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Figure 2 / Table 2 benchmark trajectory: 1952 ≈ 0.17, 1966 ≈ 0.22, 1975 ≈ 0.24, 1984 ≈ 0.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- Absolute dollar values from Table 2: 1952=34.58B, 1964=74.52B, 1975=241.70B, 1985=705.27B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>- 1984 peak is **41% higher than 1966** (the all-time high in the book period)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>- Validator `expected_range`: **[0.0, 0.3]** (registry; share_series tolerance class)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- Direction: monotonically rising throughout 1952-1985 (PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- 1964 illustration breakdown (Appendix Table 1): Group I = 28.662B, Group II = 45.88B, total T_w = 74.52B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- **Property tax coverage restricted to home-owner portion only** — renters' indirect tax burden (paid via rent) is excluded by framework design (the framework excludes tax shifting); ES1103 therefore likely understates the full property-tax burden on workers who rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- **BLS spendable-earnings comparison will show ES1103 much higher** — BLS omits state and local taxes (Bowles &amp; Gintis's $10/week 1977 estimate vs Tonak's $30.42/week, a two-thirds underestimate per note 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>- **Employer social security contribution is counted in both EC (denominator) and T_w (numerator)** — this is methodologically correct per Note 8 (pp.193-194) but may appear to inflate the rate to readers unfamiliar with the cost-to-capitalists EC definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>- **Lotteries/parimutuels is a very small Group I addition** treated as net tax (sign-inverted from BEA listing — BEA lists as expenditure but net is consistently positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- **Extension to 1986-2024 pending** Stage-4 NIPA Group I/II reconstruction (would require building a continuous concordance from current BEA NIPA tables to the 1987 paper's tax classification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **No EPR yet authored** for ES1103 (Stage 4 work)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- **Inherits S604 status**: if S604 contains synthetic or estimated rows, ES1103 inherits that status — [internal-decision-record] (No Synthetic Data Policy, 2026-05-03) does not currently list ES1103 among the five series requiring remediation, but the dependency should be re-checked after any S604 revision</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- Upstream: S604 (taxes paid by workers), S617 (employee compensation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- Companion ES series (same study): ES1101 (benefits B_w), ES1102 (government transfers G_w), ES1001, ES1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- Downstream: S607 (Net Social Wage NSW = B_w + G_w − T_w; ES1103's numerator is the T_w component); S608 (NSW/V* ratio) — both used in S901 summary table</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- Related external: Tonak (1984) PhD dissertation (underlying tax accounting framework); BEA Survey of Current Business 1981; Bowles &amp; Gintis (1985) — the "rising social wage" thesis ES1103's rising tax-rate finding refutes; Miller (1986) — the tax-incidence / tax-shifting framework ST 1987 explicitly distinguishes itself from</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>- Related project DPRs: ES1101 (benefits side of the same NSW decomposition); AS001 (social burden rate — different decomposition of the same fiscal-burden question)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/ES1103_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/N1103_research.json` on 2026-05-14; verbatim quotes added 2026-05-19 by `D4_es_ch10_13_backfill`</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); prior version of this DPR (pre-cohort-1) was a short stub with one methodology paragraph; this enrichment adds full 7-section structure with sources, reference values, known issues, cross-references; sources read = research JSON + ST 1987 full transcription + registry entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -1008,10 +1413,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1036,296 +1441,435 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Social tax rate = Taxes paid by workers to the state / Apparent wage (employee compensation). Formula: T_w / EC. This measures the fiscal burden on workers as a fraction of total employee compensation. The taxes (T_w) are composed of two groups: Group I (100% from workers): total employee compensation includes Employer and Employee Contributions for Social Insurance and Other Labor Income — the portion going to social security is treated as a direct tax on labor. Group II (allocated by labor share = total labor income / personal income): Personal Income Taxes (Federal and State); Motor Vehicle Licenses; Property Taxes restricted to the home-owner portion, further adjusted by labor share; Other Taxes and Non-Taxes. Corporate Profit Taxes, Indirect Business Taxes, and Estate and Gift Taxes are excluded as not levied on workers. An additional small category — net government receipts from lotteries and parimutuels — is treated as a positive net tax (Group I addition).</t>
+          <t>VERBATIM (ST 1987, transcription line 264-266): "Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)". This is the formal construction of the social tax numerator T_w used in ES1103. External source: Shaikh &amp; Tonak 1987, 'The Welfare State and the Myth of the Social Wage', p.187.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Taxes pp.187; Notes 8-11 pp.193-194; Key Formulas — Tax Rate; Appendix Table 1 pp.191-192)</t>
+          <t>EXTERNAL: Shaikh, Anwar and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In The Imperiled Economy, Book I, p.187. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md lines 264-266.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primary source: Shaikh and Tonak (1987). Tax rate is derived from the taxes column of Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192) divided by total employee compensation from BEA NIPA. Appendix Table 1 (p.191) illustrates the full tax calculation for 1964: Group I (social insurance contributions 28.66 + lotteries/parimutuels 0.002 = 28.662) plus Group II (personal income taxes 36.51 + other taxes 2.60 + motor vehicle 0.78 + property taxes 5.99 = 45.88), total taxes paid by labor 74.52 billion in 1964. BEA tax data from BEA (1981:121, 123, 129, 134); lotteries from BEA (1981:170).</t>
+          <t>VERBATIM (ST 1987 Figure 2 description, transcription line 324-330): "Tax Rate: 1952: ~0.17 (17%) ... Rises slowly and steadily throughout period ... 1968: ~0.22 (22%) ... 1975: ~0.24 (24%) ... 1984: ~0.31 (31%) ... By 1984: Reaches all-time high (41% higher than 1966)". These benchmark values from Figure 2 (p.188) are the primary validation targets for the ES1103 replication trajectory. External source.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 pp.191-192; Table 2 p.192; Data Sources)</t>
+          <t>EXTERNAL: Shaikh &amp; Tonak 1987, Figure 2, p.188. Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md lines 324-330.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Key benchmark values from Figure 2 time series (taxes as proportion of employee compensation): 1952 approx 17%; rises slowly and steadily throughout the period; 1966 approx 22% (benchmark reference year); 1975 approx 24%; by 1984 reaches approximately 31%, an all-time high — 41% higher than 1966. Absolute dollar values from Table 2: 1952=34.58B, 1964=74.52B, 1975=241.70B, 1985=705.27B. The tax rate shows a more monotonic upward trend compared to the benefit rate, which is why in Phase 3 (post-1975) the tax rate rise dominates the decline in the net transfer rate.</t>
+          <t>VERBATIM (ST 1987, transcription line 305): "Arguments such as those of Bowles and Gintis, which claim that 'there has been a substantial redistribution from capital to labor' over the postwar period, and which trace the current economic crisis back to a supposed increased social wage, appear to be quite ill-founded." This is the central interpretive thrust of the rising-tax-rate finding underpinning ES1103. External source.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description p.188; Table 2 p.192; Three Historical Phases pp.189-190)</t>
+          <t>EXTERNAL: Shaikh &amp; Tonak 1987, p.187 (Figure 1 implication). Verbatim from Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md line 305.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tax_classification_detail</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Group I (100% from workers — flows directly from employee compensation): Employee Contributions for Social Insurance; Employer Contributions for Social Insurance (treated as part of employee compensation cost to capitalists); Other Labor Income (pension contributions, etc.); Government-administered lotteries and parimutuels (treated as a net tax, listed as expenditure in government accounts but consistently negative net receipts). Group II (allocated by labor share): Federal Personal Income Tax; State Personal Income Tax; Motor Vehicle Licenses; Property Taxes (home-owner portion only, then × labor share); Other Taxes and Non-Taxes (passport fees, fines, etc. — very small). Excluded entirely: Corporate Profit Taxes; Indirect Business Taxes; Estate and Gift Taxes.</t>
+          <t>Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Taxes pp.187; Notes 9, 11 pp.193-194)</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Methodology, p.187</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>conceptual_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The framework traces taxes that flow directly out of employee compensation, not taxes that workers might bear through price shifting. This is explicitly distinct from the tax-incidence / tax-shifting approach used by Miller (1986). Total Employee Compensation (the apparent wage / AW) = Wages and Benefits + Employer Contributions for Social Insurance + Other Labor Income. This total is the cost to capitalists; workers' disposable income is less because social security contributions are deducted. The employer social security contribution is therefore counted as both part of EC (denominator) and part of T_w (numerator), which correctly reflects that the employer contribution is a cost of employing labor that workers bear in reduced take-home pay.</t>
+          <t>By 1984: Reaches all-time high (41% higher than 1966)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 8 p.193-194; Employee Compensation Structure section)</t>
+          <t>Shaikh &amp; Tonak 1987, Figure 2 Tax Rate, p.188</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The BLS spendable earnings series (used by Bowles and Gintis) underestimates taxes paid by workers because it deducts only Federal income and social security taxes, leaving out all state, local, and other taxes. ES1103 uses the comprehensive Tonak (1984) accounting which includes state and local taxes. Any comparison with series derived from BLS spendable earnings will show ES1103 substantially higher. The Bowles and Gintis tax estimate for 1977 was $10/week versus Tonak's $30.42/week — a two-thirds underestimate.</t>
+          <t>Tax Rate: 1952: ~0.17 (17%) ... 1968: ~0.22 (22%) ... 1975: ~0.24 (24%) ... 1984: ~0.31 (31%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 5 p.193; Notes 2-4 pp.648-650; Critique of Bowles and Gintis Methodology)</t>
+          <t>Shaikh &amp; Tonak 1987, Figure 2, p.188</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Property taxes in Group II are restricted to the home-owner portion only (not commercial/rental property taxes), which is then further scaled by labor share. This double restriction means ES1103 likely understates the full property tax burden on workers who rent rather than own, since renters effectively pay property taxes through rent but the framework excludes this indirect incidence by design (the framework excludes tax shifting).</t>
+          <t>Social tax rate = Taxes paid by workers to the state / Apparent wage (employee compensation). Formula: T_w / EC. This measures the fiscal burden on workers as a fraction of total employee compensation. The taxes (T_w) are composed of two groups: Group I (100% from workers): total employee compensation includes Employer and Employee Contributions for Social Insurance and Other Labor Income — the portion going to social security is treated as a direct tax on labor. Group II (allocated by labor share = total labor income / personal income): Personal Income Taxes (Federal and State); Motor Vehicle Licenses; Property Taxes restricted to the home-owner portion, further adjusted by labor share; Other Taxes and Non-Taxes. Corporate Profit Taxes, Indirect Business Taxes, and Estate and Gift Taxes are excluded as not levied on workers. An additional small category — net government receipts from lotteries and parimutuels — is treated as a positive net tax (Group I addition).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote d; Classification of Taxes)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Taxes pp.187; Notes 8-11 pp.193-194; Key Formulas — Tax Rate; Appendix Table 1 pp.191-192)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The steady upward trend in the tax rate (from ~17% in 1952 to ~31% in 1984) reflects growth in social security contributions and rising personal income tax rates. Reagan-era tax cuts (income tax reductions) were offset by continuing growth in social security contributions. By 1985 the tax rate reached 41% above its 1966 level despite income tax rate cuts, illustrating that the social security component dominates the long-run trend. ES1103 should not be interpreted as solely reflecting income tax policy.</t>
+          <t>Primary source: Shaikh and Tonak (1987). Tax rate is derived from the taxes column of Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192) divided by total employee compensation from BEA NIPA. Appendix Table 1 (p.191) illustrates the full tax calculation for 1964: Group I (social insurance contributions 28.66 + lotteries/parimutuels 0.002 = 28.662) plus Group II (personal income taxes 36.51 + other taxes 2.60 + motor vehicle 0.78 + property taxes 5.99 = 45.88), total taxes paid by labor 74.52 billion in 1964. BEA tax data from BEA (1981:121, 123, 129, 134); lotteries from BEA (1981:170).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description p.188; Phase 3 analysis pp.189-190)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 pp.191-192; Table 2 p.192; Data Sources)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEC-012 (No Synthetic Data Policy, 2026-05-03): ES1103 is not listed among the five series requiring synthetic-data remediation. However, if S604 (taxes paid by workers) contains synthetic or estimated data, ES1103 inherits that status. The 34-year series in S&amp;T (1987) Table 2 column 2 (taxes column) provides direct validation benchmarks for P19 S604 output.</t>
+          <t>Key benchmark values from Figure 2 time series (taxes as proportion of employee compensation): 1952 approx 17%; rises slowly and steadily throughout the period; 1966 approx 22% (benchmark reference year); 1975 approx 24%; by 1984 reaches approximately 31%, an all-time high — 41% higher than 1966. Absolute dollar values from Table 2: 1952=34.58B, 1964=74.52B, 1975=241.70B, 1985=705.27B. The tax rate shows a more monotonic upward trend compared to the benefit rate, which is why in Phase 3 (post-1975) the tax rate rise dominates the decline in the net transfer rate.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description p.188; Table 2 p.192; Three Historical Phases pp.189-190)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tax_classification_detail</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Group I (100% from workers — flows directly from employee compensation): Employee Contributions for Social Insurance; Employer Contributions for Social Insurance (treated as part of employee compensation cost to capitalists); Other Labor Income (pension contributions, etc.); Government-administered lotteries and parimutuels (treated as a net tax, listed as expenditure in government accounts but consistently negative net receipts). Group II (allocated by labor share): Federal Personal Income Tax; State Personal Income Tax; Motor Vehicle Licenses; Property Taxes (home-owner portion only, then × labor share); Other Taxes and Non-Taxes (passport fees, fines, etc. — very small). Excluded entirely: Corporate Profit Taxes; Indirect Business Taxes; Estate and Gift Taxes.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Classification of Taxes pp.187; Notes 9, 11 pp.193-194)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>conceptual_note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Social tax rate = T_w / EC, 1952-1985 (34 years). Taxes include social security contributions from employee compensation (Group I, 100%) plus labor share of personal taxes (Group II). Excludes corporate, indirect, and estate taxes. Key characteristic: monotonically rising trend throughout the period, reaching 41% above 1966 level by 1984.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>The framework traces taxes that flow directly out of employee compensation, not taxes that workers might bear through price shifting. This is explicitly distinct from the tax-incidence / tax-shifting approach used by Miller (1986). Total Employee Compensation (the apparent wage / AW) = Wages and Benefits + Employer Contributions for Social Insurance + Other Labor Income. This total is the cost to capitalists; workers' disposable income is less because social security contributions are deducted. The employer social security contribution is therefore counted as both part of EC (denominator) and part of T_w (numerator), which correctly reflects that the employer contribution is a cost of employing labor that workers bear in reduced take-home pay.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 8 p.193-194; Employee Compensation Structure section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The BLS spendable earnings series (used by Bowles and Gintis) underestimates taxes paid by workers because it deducts only Federal income and social security taxes, leaving out all state, local, and other taxes. ES1103 uses the comprehensive Tonak (1984) accounting which includes state and local taxes. Any comparison with series derived from BLS spendable earnings will show ES1103 substantially higher. The Bowles and Gintis tax estimate for 1977 was $10/week versus Tonak's $30.42/week — a two-thirds underestimate.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 5 p.193; Notes 2-4 pp.648-650; Critique of Bowles and Gintis Methodology)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Property taxes in Group II are restricted to the home-owner portion only (not commercial/rental property taxes), which is then further scaled by labor share. This double restriction means ES1103 likely understates the full property tax burden on workers who rent rather than own, since renters effectively pay property taxes through rent but the framework excludes this indirect incidence by design (the framework excludes tax shifting).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Appendix Table 1 footnote d; Classification of Taxes)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Property tax coverage restricted to home-owner portion only — renters' indirect tax burden excluded by framework design</t>
+          <t>The steady upward trend in the tax rate (from ~17% in 1952 to ~31% in 1984) reflects growth in social security contributions and rising personal income tax rates. Reagan-era tax cuts (income tax reductions) were offset by continuing growth in social security contributions. By 1985 the tax rate reached 41% above its 1966 level despite income tax rate cuts, illustrating that the social security component dominates the long-run trend. ES1103 should not be interpreted as solely reflecting income tax policy.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Figure 2 description p.188; Phase 3 analysis pp.189-190)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BLS spendable earnings comparison will show ES1103 much higher (BLS omits state/local taxes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Employer social security contribution is counted in both EC (denominator) and T_w (numerator) — this is methodologically correct but may appear to inflate the rate</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] (No Synthetic Data Policy, 2026-05-03): ES1103 is not listed among the five series requiring synthetic-data remediation. However, if S604 (taxes paid by workers) contains synthetic or estimated data, ES1103 inherits that status. The 34-year series in S&amp;T (1987) Table 2 column 2 (taxes column) provides direct validation benchmarks for P19 S604 output.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Lotteries/parimutuels is a very small addition treated as net tax (sign-inverted from BEA listing)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Taxes (from workers): = Group I (Social Security contributions from employee compensation) + Labor's share of Group II (personal taxes)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>By 1984: Reaches all-time high (41% higher than 1966)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Tax Rate: 1952: ~0.17 (17%) ... 1968: ~0.22 (22%) ... 1975: ~0.24 (24%) ... 1984: ~0.31 (31%)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Social tax rate = T_w / EC, 1952-1985 (34 years). Taxes include social security contributions from employee compensation (Group I, 100%) plus labor share of personal taxes (Group II). Excludes corporate, indirect, and estate taxes. Key characteristic: monotonically rising trend throughout the period, reaching 41% above 1966 level by 1984.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Property tax coverage restricted to home-owner portion only — renters' indirect tax burden excluded by framework design</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BLS spendable earnings comparison will show ES1103 much higher (BLS omits state/local taxes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Employer social security contribution is counted in both EC (denominator) and T_w (numerator) — this is methodologically correct but may appear to inflate the rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lotteries/parimutuels is a very small addition treated as net tax (sign-inverted from BEA listing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ES1001</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>ES1002</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>ES1101</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>ES1102</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
         <is>
           <t>S604</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ST_1987</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In Robert Cherry et al. (eds.), The Imperiled Economy, Book I. New York: Union for Radical Political Economics, pp. 184-194.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>BEA_1981</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1981. Survey of Current Business. Tables at pp. 121, 123, 129, 134 (tax data); p. 170 (lotteries/parimutuels).</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Tonak_1984</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Tonak, Ertugrul Ahmet. 1984. 'A Conceptualization of State Revenues and Expenditures U.S.: 1952-1980.' PhD Dissertation, New School for Social Research. UMI Order Number 9414212.</t>
         </is>
@@ -1342,11 +1886,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1413,7 +1957,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": 0.17, "1968": 0.22, "1975": 0.24, "1984": 0.31}</t>
         </is>
       </c>
     </row>
@@ -1458,7 +2002,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
